--- a/ig/document/StructureDefinition-medcom-document-practitioner.xlsx
+++ b/ig/document/StructureDefinition-medcom-document-practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-14T10:37:57+00:00</t>
+    <t>2026-03-10T10:54:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1899,7 +1899,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>86</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>115</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>140</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>148</v>
       </c>
@@ -3263,7 +3263,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>170</v>
       </c>
@@ -3835,7 +3835,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>201</v>
       </c>
@@ -3951,7 +3951,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>211</v>
       </c>
@@ -4409,7 +4409,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>246</v>
       </c>
@@ -4983,7 +4983,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>276</v>
       </c>
@@ -5097,7 +5097,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>285</v>
       </c>
@@ -8053,12 +8053,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN56">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/ig/document/StructureDefinition-medcom-document-practitioner.xlsx
+++ b/ig/document/StructureDefinition-medcom-document-practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T10:54:08+00:00</t>
+    <t>2026-04-29T08:07:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
